--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611560</v>
+        <v>611559</v>
       </c>
       <c r="R19" t="n">
         <v>7239997</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611560</v>
+        <v>611559</v>
       </c>
       <c r="R37" t="n">
         <v>7239997</v>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R19" t="n">
         <v>7239997</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R37" t="n">
         <v>7239997</v>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135811430</v>
       </c>
       <c r="B2" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135812023</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135811950</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135812122</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135812223</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135812299</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>135816300</v>
       </c>
       <c r="B15" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135812576</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135812635</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135812821</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>135813298</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>135813658</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135813853</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135813922</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135813955</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135815124</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135816309</v>
       </c>
       <c r="B25" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>135812551</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135813037</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135813343</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135813936</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135813986</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135814151</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>135812532</v>
       </c>
       <c r="B32" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135812023</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>135816300</v>
       </c>
       <c r="B15" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135812576</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135812635</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135812821</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>135813298</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>135813658</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135813853</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135813922</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135813955</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135815124</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135816309</v>
       </c>
       <c r="B25" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111269</v>
+        <v>111270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R19" t="n">
         <v>7239997</v>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111269</v>
+        <v>111270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R37" t="n">
         <v>7239997</v>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135811430</v>
       </c>
       <c r="B2" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135812023</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135811950</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135812122</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135812223</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135812299</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>135816300</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135812576</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135812635</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135812821</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>135813298</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611560</v>
+        <v>611559</v>
       </c>
       <c r="R19" t="n">
         <v>7239997</v>
@@ -2544,7 +2544,7 @@
         <v>135813658</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135813853</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135813922</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135813955</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135815124</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135816309</v>
       </c>
       <c r="B25" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>135812551</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135813037</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135813343</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135813936</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135813986</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135814151</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>135812532</v>
       </c>
       <c r="B32" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611560</v>
+        <v>611559</v>
       </c>
       <c r="R37" t="n">
         <v>7239997</v>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135811430</v>
       </c>
       <c r="B2" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135812023</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135811950</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135812122</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135812223</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135812299</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>135816300</v>
       </c>
       <c r="B15" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135812576</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135812635</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135812821</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>135813298</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R19" t="n">
         <v>7239997</v>
@@ -2544,7 +2544,7 @@
         <v>135813658</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135813853</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135813922</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135813955</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135815124</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135816309</v>
       </c>
       <c r="B25" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>135812551</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135813037</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135813343</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135813936</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135813986</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135814151</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>135812532</v>
       </c>
       <c r="B32" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611559</v>
+        <v>611560</v>
       </c>
       <c r="R37" t="n">
         <v>7239997</v>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 17324-2024 artfynd.xlsx
+++ b/artfynd/A 17324-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135811430</v>
       </c>
       <c r="B2" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135811457</v>
       </c>
       <c r="B3" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135811773</v>
       </c>
       <c r="B4" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135812023</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135811950</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135812122</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135812223</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135812299</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>135811795</v>
       </c>
       <c r="B10" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>135811809</v>
       </c>
       <c r="B11" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>135811823</v>
       </c>
       <c r="B12" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>135812195</v>
       </c>
       <c r="B13" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135812434</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>135816300</v>
       </c>
       <c r="B15" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>135812576</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>135812635</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135812821</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>135813298</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>135813658</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135813853</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135813922</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>135813955</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>135815124</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135816309</v>
       </c>
       <c r="B25" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>135812551</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>135813037</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>135813343</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>135813936</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135813986</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>135814151</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>135812532</v>
       </c>
       <c r="B32" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>135812664</v>
       </c>
       <c r="B33" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>135814491</v>
       </c>
       <c r="B34" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>135812594</v>
       </c>
       <c r="B35" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>135816256</v>
       </c>
       <c r="B36" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>135813263</v>
       </c>
       <c r="B37" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>135815677</v>
       </c>
       <c r="B38" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>135813569</v>
       </c>
       <c r="B39" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
